--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0130.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0130.xlsx
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Thật lòng, cái này trông còn khá hơn mấy thứ cậu vẫn dùng... Khoan, ta hiểu rồi. Cậu chỉ đang trêu ta để gây chuyện phải không?</t>
+          <t>Thật lòng, cái này trông còn khá hơn mấy thứ cậu vẫn dùng... Khoan, tao hiểu rồi. Cậu chỉ đang trêu tao để gây chuyện phải không?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Ồ, vậy giờ lỗi là do ta hả?!</t>
+          <t>Ồ, vậy giờ lỗi là do tao hả?!</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Thật mà, ta chỉ ra đây dòm ngó chơi cho vui thôi! Ai ngờ lại dính vào một truyền thuyết đô thị thật sự...</t>
+          <t>Thật mà, tao chỉ ra đây dòm ngó chơi cho vui thôi! Ai ngờ lại dính vào một truyền thuyết đô thị thật sự...</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Ta thấy không ổn. Không phải lạnh, chỉ là... mơ hồ thế nào ấy.</t>
+          <t>Tao thấy không ổn. Không phải lạnh, chỉ là... mơ hồ thế nào ấy.</t>
         </is>
       </c>
     </row>
@@ -19034,7 +19034,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Sao cậu biết?</t>
+          <t>Sao cậu biết được?</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Ừm... Đúng như ta nghĩ. Đây không chỉ là dữ liệu lạc. ICE-Δ-013. Các giao thức xác minh vẫn còn hoạt động. Và... ơ. Một trong các liên kết yêu cầu vẫn còn nóng hả.</t>
+          <t>Ừm... Đúng như tao nghĩ. Đây không chỉ là dữ liệu lạc. ICE-Δ-013. Các giao thức xác minh vẫn còn hoạt động. Và... ơ. Một trong các liên kết yêu cầu vẫn còn nóng hả.</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Ừ. Ta sẽ cắt đứt hết những kết nối còn sót lại của nó với hệ thống. Dứt điểm vòng lặp.</t>
+          <t>Ừ. Tao sẽ cắt đứt hết những kết nối còn sót lại của nó với hệ thống. Dứt điểm vòng lặp.</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Ừm... Đúng như ta nghĩ. Đây không chỉ là dữ liệu lạc. ICE-Δ-013. Các giao thức xác minh vẫn còn hoạt động. Và... ơ. Một trong các liên kết yêu cầu vẫn còn nóng hả.</t>
+          <t>Ừm... Đúng như tao nghĩ. Đây không chỉ là dữ liệu lạc. ICE-Δ-013. Các giao thức xác minh vẫn còn hoạt động. Và... ơ. Một trong các liên kết yêu cầu vẫn còn nóng hả.</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Ừ. Ta sẽ cắt đứt hết những kết nối còn sót lại của nó với hệ thống. Dứt điểm vòng lặp.</t>
+          <t>Ừ. Tao sẽ cắt đứt hết những kết nối còn sót lại của nó với hệ thống. Dứt điểm vòng lặp.</t>
         </is>
       </c>
     </row>
@@ -26509,7 +26509,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Dù chỉ là để ta xác nhận nhịp thở của ngươi có thay đổi không, cũng hãy nhớ quay lại thăm ta nhé.</t>
+          <t>Dù chỉ là để tao xác nhận nhịp thở của mày có thay đổi không, cũng hãy nhớ quay lại thăm tao nhé.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>...Ừ. Ta hiểu rồi.</t>
+          <t>...Ừ. Tao hiểu rồi.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Ừ. Nhưng ta thực sự không muốn.</t>
+          <t>Ừ. Nhưng tao thực sự không muốn.</t>
         </is>
       </c>
     </row>
@@ -28394,7 +28394,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Một khi ta nộp cái này, mọi người sẽ hỏi vụ dị thường này bắt đầu từ khi nào.</t>
+          <t>Một khi tao nộp cái này, mọi người sẽ hỏi vụ dị thường này bắt đầu từ khi nào.</t>
         </is>
       </c>
     </row>
@@ -28914,7 +28914,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Ta không biết tọa độ chính xác. Hệ thống định vị ban đầu vẫn hoạt động tốt, nhưng rồi toàn bộ giao diện bị loạn hết.</t>
+          <t>Tao không biết tọa độ chính xác. Hệ thống định vị ban đầu vẫn hoạt động tốt, nhưng rồi toàn bộ giao diện bị loạn hết.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
